--- a/docs/downloads/scope-document.xlsx
+++ b/docs/downloads/scope-document.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>e.g., LangGraph</t>
+          <t>e.g., the agent framework your team has chosen (see Stage 4: Choose a Platform)</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>e.g., Claude API via Anthropic SDK</t>
+          <t>e.g., the language model your team has approved, accessed via its official API</t>
         </is>
       </c>
     </row>
